--- a/docs/downloads/经营分_鲁东省区__日照片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__日照片区_2026-10-18.xlsx
@@ -1329,7 +1329,7 @@
         <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7110793810954848260</t>
+          <t>7255908718809647167</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>非繁城品(日照万平口灯塔景区店）</t>
+          <t>白玉兰（商务）酒店日照莒县古城店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>非繁城品(日照万平口灯塔景区店)</t>
+          <t>白玉兰酒店(日照莒县古城店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1681,7 +1681,7 @@
         <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6832211688859650059</t>
+          <t>7110793810954848260</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>麗枫酒店（日照港万平口灯塔景区店）</t>
+          <t>非繁城品(日照万平口灯塔景区店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>麗枫酒店(日照港灯塔景区北京路店)</t>
+          <t>非繁城品(日照万平口灯塔景区店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2187,22 +2187,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7255908718809647167</t>
+          <t>7378729592419026970</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>白玉兰（商务）酒店日照莒县古城店</t>
+          <t>维也纳酒店(日照万平口东夷小镇店)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>白玉兰酒店(日照莒县古城店)</t>
+          <t>维也纳酒店(日照万平口东夷小镇店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2275,17 +2275,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7378729592419026970</t>
+          <t>6601132668430059533</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店(日照万平口东夷小镇店)</t>
+          <t>麗枫酒店（日照万平口风景区店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(日照万平口东夷小镇店)</t>
+          <t>麗枫酒店(日照万平口风景区店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2311,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2323,7 +2323,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2363,33 +2363,33 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601132668430059533</t>
+          <t>6962135286033762308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>麗枫酒店（日照万平口风景区店）</t>
+          <t>麗枫酒店（日照岚山多岛海景区店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>麗枫酒店(日照万平口风景区店)</t>
+          <t>麗枫酒店(日照岚山多岛海景区店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2399,19 +2399,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6962135286033762308</t>
+          <t>6832211688859650059</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>麗枫酒店（日照岚山多岛海景区店）</t>
+          <t>麗枫酒店（日照港万平口灯塔景区店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>麗枫酒店(日照岚山多岛海景区店)</t>
+          <t>麗枫酒店(日照港灯塔景区北京路店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2473,11 +2473,11 @@
         <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2493,13 +2493,13 @@
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -3155,33 +3155,33 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6859686143806441485</t>
+          <t>6700819606694676487</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>喆啡酒店（日照万平口灯塔景区店）</t>
+          <t>维也纳3好酒店(山东日照站万平口灯塔景区店)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>喆啡酒店(日照万平口灯塔景区店)</t>
+          <t>维也纳3好酒店(山东日照万平口灯塔景区店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3197,7 +3197,7 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
@@ -3243,29 +3243,29 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7226273190496962615</t>
+          <t>6859686143806441485</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>日照岚山多岛海非繁云居酒店</t>
+          <t>喆啡酒店（日照万平口灯塔景区店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>日照岚山多岛海云居酒店</t>
+          <t>喆啡酒店(日照万平口灯塔景区店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>110</v>
       </c>
       <c r="I31" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6700819606694676487</t>
+          <t>7226273190496962615</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山东日照站万平口灯塔景区店)</t>
+          <t>日照岚山多岛海非繁云居酒店</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山东日照万平口灯塔景区店)</t>
+          <t>日照岚山多岛海云居酒店</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I32" t="n">
         <v>5</v>
@@ -3379,7 +3379,7 @@
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
